--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,53 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INC-2026-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>11:26 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ternium México</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0301682984</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TX6793212</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Jesus Morales</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,53 +460,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>INC-2026-0001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>11:26 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ternium México</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0301682984</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TX6793212</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Jesus Morales</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Aceptado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,53 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INC-2026-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>12:03 AM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ACEROMEX</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0301682984</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TX6793212</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Jesus Morales</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,53 +460,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>INC-2026-0001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>12:03 AM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ACEROMEX</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0301682984</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TX6793212</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Jesus Morales</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Aceptado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,53 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INC-2026-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>02:17 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ACEROMEX</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2603-1752 ACEROMEX JMC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CPQ-888698</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Jesus Morales</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,53 +460,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>INC-2026-0001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>02:17 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ACEROMEX</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2603-1752 ACEROMEX JMC</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CPQ-888698</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Jesus Morales</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Aceptado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,53 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INC-2026-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>02:47 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ACEROMEX</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2603-1752 ACEROMEX JMC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TX6793212</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Jesus Morales</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,53 +460,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>INC-2026-0001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>02:47 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ACEROMEX</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2603-1752 ACEROMEX JMC</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TX6793212</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Jesus Morales</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Aceptado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,53 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INC-2026-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>03:06 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ACEROMEX</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2603-1752 ACEROMEX JMC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TX6793212</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Jesus Morales</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,53 +460,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>INC-2026-0001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>03:06 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ACEROMEX</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2603-1752 ACEROMEX JMC</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TX6793212</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Jesus Morales</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Aceptado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,53 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INC-2026-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>03:16 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ACEROMEX</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2603-1752 ACEROMEX JMC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CPQ-888698.pdf</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Jesus Morales</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,53 +460,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>INC-2026-0001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>03:16 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ACEROMEX</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2603-1752 ACEROMEX JMC</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CPQ-888698.pdf</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Jesus Morales</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Aceptado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,53 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INC-2026-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>03:51 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ACEROMEX</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0301682984</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TX6793212</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Jesus Morales</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,53 +460,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>INC-2026-0001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>03:51 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ACEROMEX</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0301682984</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TX6793212</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Jesus Morales</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Aceptado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,53 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INC-2026-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>10:19 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ACEROMEX</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2603-1752 ACEROMEX JMC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CPQ-888698</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Miguel Ramos</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Condicionado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,53 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>INC-2026-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>03:55 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ACEROMEX</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2603-1752</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CPQ-888698</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Miguel Ramos</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Condicionado</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0002/Dosier_Calidad_INC-2026-0002.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,17 +466,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INC-2026-0001</t>
+          <t>INC-2026-0002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10:19 PM</t>
+          <t>03:55 PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2603-1752 ACEROMEX JMC</t>
+          <t>2603-1752</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -505,53 +505,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>INC-2026-0002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>03:55 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ACEROMEX</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2603-1752</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CPQ-888698</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Miguel Ramos</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Condicionado</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0002/Dosier_Calidad_INC-2026-0002.pdf</t>
         </is>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,53 +460,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>INC-2026-0002</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>03:55 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ACEROMEX</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2603-1752</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CPQ-888698</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Miguel Ramos</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Condicionado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0002/Dosier_Calidad_INC-2026-0002.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,53 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INC-2026-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>04:16 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ACEROMEX</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2603-1752 ACEROMEX JMC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CPQ-888698</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Miguel Ramos</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Condicionado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,53 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>INC-2026-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>04:22 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ACEROMEX</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2603-1752 ACEROMEX JMC</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CPQ-888698</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Miguel Ramos</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Condicionado</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0002/Dosier_Calidad_INC-2026-0002.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +554,53 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0002/Dosier_Calidad_INC-2026-0002.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>INC-2026-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>04:27 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ACEROMEX</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2603-1752 ACEROMEX JMC</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CPQ-888698</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Miguel Ramos</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0003/Dosier_Calidad_INC-2026-0003.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INC-2026-0001</t>
+          <t>INC-2026-0002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -476,7 +476,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>04:16 PM</t>
+          <t>04:22 PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -506,14 +506,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0002/Dosier_Calidad_INC-2026-0002.pdf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INC-2026-0002</t>
+          <t>INC-2026-0003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>04:22 PM</t>
+          <t>04:27 PM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -548,57 +548,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Condicionado</t>
+          <t>Aceptado</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0002/Dosier_Calidad_INC-2026-0002.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>INC-2026-0003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>04:27 PM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ACEROMEX</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2603-1752 ACEROMEX JMC</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CPQ-888698</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Miguel Ramos</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Aceptado</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0003/Dosier_Calidad_INC-2026-0003.pdf</t>
         </is>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INC-2026-0002</t>
+          <t>INC-2026-0003</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -476,7 +476,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>04:22 PM</t>
+          <t>04:27 PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -501,57 +501,10 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Condicionado</t>
+          <t>Aceptado</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0002/Dosier_Calidad_INC-2026-0002.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>INC-2026-0003</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>04:27 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ACEROMEX</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2603-1752 ACEROMEX JMC</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CPQ-888698</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Miguel Ramos</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Aceptado</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0003/Dosier_Calidad_INC-2026-0003.pdf</t>
         </is>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,53 +460,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>INC-2026-0003</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>04:27 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ACEROMEX</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2603-1752 ACEROMEX JMC</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CPQ-888698</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Miguel Ramos</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Aceptado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0003/Dosier_Calidad_INC-2026-0003.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,53 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Dossier_Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INC-2026-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>06:06 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ACEROMEX</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2603-1752 ACEROMEX JMC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CPQ-888698</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Miguel Ramos</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Condicionado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,53 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0001/Dosier_Calidad_INC-2026-0001.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>INC-2026-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>06:12 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ACEROMEX</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2603-1752 ACEROMEX JMC</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CPQ-888698</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Miguel Ramos</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0002/Dosier_Calidad_INC-2026-0002.pdf</t>
         </is>
       </c>
     </row>

--- a/BD_Reportes_Incoming.xlsx
+++ b/BD_Reportes_Incoming.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recepciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recepciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +554,53 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0002/Dosier_Calidad_INC-2026-0002.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>INC-2026-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>03:03 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Steel Technologies</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>26031911</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>P509122-1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Miguel Ramos</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>/mount/src/incoming-calidad/carpetas_electronicas/INC-2026-0003/Dosier_Calidad_INC-2026-0003.pdf</t>
         </is>
       </c>
     </row>
